--- a/data/trans_dic/P21D_5_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21D_5_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,39</t>
+          <t>0,0; 0,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,25</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,49</t>
+          <t>0,39; 3,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,59</t>
+          <t>0,25; 2,5</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,86</t>
+          <t>0,16; 1,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,02; 0,82</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,54</t>
+          <t>0,04; 0,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,74</t>
+          <t>0,19; 0,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,48</t>
+          <t>0,16; 0,49</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1921</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1036</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1392</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5976</t>
+          <t>0; 5227</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 920</t>
+          <t>0; 715</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98; 5612</t>
+          <t>0; 5178</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4222</t>
+          <t>0; 4189</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>547; 5081</t>
+          <t>571; 5495</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>679; 6236</t>
+          <t>592; 6002</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6648</t>
+          <t>0; 6235</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1696</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7332</t>
+          <t>0; 6469</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1243</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1950</t>
+          <t>0; 1868</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1857</t>
+          <t>0; 1821</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1354</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1059</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1201</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2098</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4337</t>
+          <t>0; 4550</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4773</t>
+          <t>0; 4089</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3183</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>576; 6474</t>
+          <t>568; 6047</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 6956</t>
+          <t>148; 7417</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>789; 8912</t>
+          <t>698; 9228</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2884; 11779</t>
+          <t>2979; 11657</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4642; 15567</t>
+          <t>5164; 16093</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_5_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21D_5_R-Provincia-trans_dic.xlsx
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,3</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,78</t>
+          <t>0,39; 3,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,5</t>
+          <t>0,27; 2,64</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,82</t>
+          <t>0,08; 1,05</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,55</t>
+          <t>0,06; 0,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,73</t>
+          <t>0,2; 0,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,49</t>
+          <t>0,17; 0,51</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>595</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1590</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5227</t>
+          <t>0; 4331</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 715</t>
+          <t>0; 3637</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5178</t>
+          <t>0; 6558</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2518</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4189</t>
+          <t>0; 2988</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>571; 5495</t>
+          <t>567; 5482</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>592; 6002</t>
+          <t>643; 6320</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6235</t>
+          <t>0; 6638</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6469</t>
+          <t>0; 6738</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1868</t>
+          <t>0; 1691</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1821</t>
+          <t>0; 2292</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1395</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4550</t>
+          <t>0; 5486</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4089</t>
+          <t>0; 4500</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2445</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>568; 6047</t>
+          <t>649; 7076</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>148; 7417</t>
+          <t>648; 8051</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10064</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>698; 9228</t>
+          <t>989; 8574</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2979; 11657</t>
+          <t>3369; 12548</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5164; 16093</t>
+          <t>5702; 16740</t>
         </is>
       </c>
     </row>
